--- a/notebooks/Raw_Data_Ventas.xlsx
+++ b/notebooks/Raw_Data_Ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilso\Desktop\ll-2026\BIIG DATA\PARCIAL 1\bigdata-primer-parcial\notebooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4947ECFA-B376-4901-AC33-04CD6AF1F7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF07B7B6-31C6-4777-A9DD-B478AF992360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
